--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2337" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2522" uniqueCount="524">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -438,33 +438,130 @@
     <t>DiagnosticReport.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension:extension-DiagnosticReport-note</t>
+  </si>
+  <si>
+    <t>extension-DiagnosticReport-note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://va.gov/fhir/StructureDefinition/extension-DiagnosticReport-note}
+</t>
+  </si>
+  <si>
+    <t>R5 pre-adopt for http://hl7.org/fhir/5.0/StructureDefinition/extension-DiagnosticReport.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension:extension-DiagnosticReport-note.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension:extension-DiagnosticReport-note.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension:extension-DiagnosticReport-note.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/StructureDefinition/extension-DiagnosticReport-note</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension:extension-DiagnosticReport-note.value[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>1442: source value from MICROBIOLOGY - BACT RPT REMARK &gt; BACT RPT REMARK - BACT RPT REMARK (63.05-13 &gt; 63.33-.01)</t>
+  </si>
+  <si>
+    <t>Micro.BacteriologyReports.BacteriologyReportRemark</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -472,6 +569,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -516,39 +616,13 @@
     <t>DiagnosticReport.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DiagnosticReport.identifier.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>DiagnosticReport.identifier.use</t>
@@ -1897,12 +1971,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP60"/>
+  <dimension ref="A1:AP65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="66.875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.1328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="31.30859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2918,7 +2992,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2937,17 +3011,15 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>82</v>
@@ -2984,16 +3056,14 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>141</v>
@@ -3023,7 +3093,7 @@
         <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>82</v>
@@ -3034,43 +3104,41 @@
         <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L10" t="s" s="2">
-        <v>144</v>
-      </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O10" t="s" s="2">
         <v>146</v>
       </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3118,7 +3186,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3127,7 +3195,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -3145,7 +3213,7 @@
         <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>82</v>
@@ -3156,18 +3224,18 @@
         <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>82</v>
@@ -3176,7 +3244,7 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
         <v>150</v>
@@ -3187,12 +3255,8 @@
       <c r="M11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="N11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3240,19 +3304,19 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
@@ -3261,24 +3325,24 @@
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3289,7 +3353,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -3301,13 +3365,13 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3346,31 +3410,31 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>82</v>
@@ -3385,7 +3449,7 @@
         <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -3393,21 +3457,21 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3419,16 +3483,16 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3436,7 +3500,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>82</v>
@@ -3466,31 +3530,31 @@
         <v>82</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>82</v>
@@ -3505,7 +3569,7 @@
         <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>82</v>
@@ -3513,10 +3577,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3530,29 +3594,25 @@
         <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3576,13 +3636,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3600,7 +3660,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3615,19 +3675,19 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3635,45 +3695,45 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3698,13 +3758,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3722,19 +3782,19 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3746,10 +3806,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>191</v>
+        <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3757,24 +3817,24 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
@@ -3783,19 +3843,19 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3805,10 +3865,10 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>82</v>
@@ -3844,13 +3904,13 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -3859,30 +3919,30 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>82</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3896,26 +3956,24 @@
         <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>151</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3928,7 +3986,7 @@
         <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -3964,7 +4022,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>153</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3976,10 +4034,10 @@
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
@@ -3988,10 +4046,10 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -3999,21 +4057,21 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -4022,18 +4080,20 @@
         <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>213</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4070,31 +4130,31 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4106,10 +4166,10 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -4117,10 +4177,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4137,24 +4197,26 @@
         <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>220</v>
+        <v>111</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4178,13 +4240,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -4202,7 +4264,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4226,10 +4288,10 @@
         <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4237,45 +4299,45 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4300,13 +4362,13 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>82</v>
+        <v>211</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4324,13 +4386,13 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
@@ -4339,19 +4401,19 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>234</v>
+        <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4359,10 +4421,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4370,7 +4432,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4379,23 +4441,25 @@
         <v>92</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="O21" t="s" s="2">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4405,10 +4469,10 @@
         <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>82</v>
+        <v>222</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>82</v>
@@ -4420,11 +4484,13 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4442,56 +4508,56 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>92</v>
@@ -4503,16 +4569,16 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4526,7 +4592,7 @@
         <v>82</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>82</v>
@@ -4538,35 +4604,37 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>257</v>
+        <v>82</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -4575,7 +4643,7 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
@@ -4584,21 +4652,21 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4618,16 +4686,16 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>160</v>
+        <v>237</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>161</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>162</v>
+        <v>239</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4678,7 +4746,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4690,7 +4758,7 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -4702,10 +4770,10 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>82</v>
+        <v>241</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>164</v>
+        <v>242</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4713,21 +4781,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4736,19 +4804,19 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>137</v>
+        <v>244</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>138</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>140</v>
+        <v>247</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4786,31 +4854,31 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>170</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -4822,10 +4890,10 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>164</v>
+        <v>250</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4833,14 +4901,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4850,28 +4918,28 @@
         <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4920,7 +4988,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4935,19 +5003,19 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4955,10 +5023,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4966,7 +5034,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>91</v>
@@ -4975,25 +5043,23 @@
         <v>92</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5018,13 +5084,11 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5042,58 +5106,56 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>92</v>
@@ -5105,16 +5167,16 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5125,7 +5187,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -5140,31 +5202,29 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5179,7 +5239,7 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -5188,54 +5248,52 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>262</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>151</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5260,13 +5318,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5284,10 +5342,10 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>153</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>91</v>
@@ -5296,7 +5354,7 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5305,35 +5363,35 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>297</v>
+        <v>154</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5345,15 +5403,17 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5390,31 +5450,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5429,7 +5489,7 @@
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5437,14 +5497,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5460,21 +5520,23 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>137</v>
+        <v>290</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>138</v>
+        <v>291</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>166</v>
+        <v>292</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5510,19 +5572,19 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>170</v>
+        <v>295</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5534,7 +5596,7 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -5546,10 +5608,10 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>164</v>
+        <v>297</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5557,10 +5619,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5571,7 +5633,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>92</v>
@@ -5583,19 +5645,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>266</v>
+        <v>150</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5644,13 +5706,13 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
@@ -5659,19 +5721,19 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5679,41 +5741,45 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5723,7 +5789,7 @@
         <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>82</v>
@@ -5738,13 +5804,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5762,22 +5828,22 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -5786,53 +5852,53 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>164</v>
+        <v>285</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>136</v>
+        <v>313</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>137</v>
+        <v>206</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>138</v>
+        <v>314</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>166</v>
+        <v>315</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>140</v>
+        <v>316</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5858,43 +5924,43 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>82</v>
+        <v>211</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>170</v>
+        <v>312</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5903,24 +5969,24 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>164</v>
+        <v>321</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5934,29 +6000,25 @@
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>151</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -5965,7 +6027,7 @@
         <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>82</v>
@@ -6004,7 +6066,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>311</v>
+        <v>153</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6016,10 +6078,10 @@
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
@@ -6028,10 +6090,10 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>314</v>
+        <v>154</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6039,21 +6101,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6062,19 +6124,19 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>193</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>317</v>
+        <v>194</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>318</v>
+        <v>177</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6112,31 +6174,31 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>319</v>
+        <v>158</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6148,10 +6210,10 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>321</v>
+        <v>154</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6159,10 +6221,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6173,7 +6235,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>92</v>
@@ -6185,17 +6247,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>111</v>
+        <v>290</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>291</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6244,13 +6308,13 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
@@ -6259,19 +6323,19 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6279,10 +6343,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6296,27 +6360,25 @@
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>331</v>
+        <v>151</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>332</v>
+        <v>152</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>333</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6364,7 +6426,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>334</v>
+        <v>153</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6376,22 +6438,22 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>337</v>
+        <v>154</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6399,21 +6461,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6422,23 +6484,21 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>339</v>
+        <v>136</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>340</v>
+        <v>193</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>341</v>
+        <v>194</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6474,31 +6534,31 @@
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>344</v>
+        <v>158</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6510,10 +6570,10 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>346</v>
+        <v>154</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6521,10 +6581,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6547,19 +6607,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>278</v>
+        <v>333</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6569,7 +6629,7 @@
         <v>82</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>82</v>
@@ -6608,7 +6668,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>279</v>
+        <v>335</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6623,19 +6683,19 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>283</v>
+        <v>338</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6643,24 +6703,24 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
@@ -6669,18 +6729,18 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>352</v>
+        <v>150</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6728,7 +6788,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6743,34 +6803,34 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6780,7 +6840,7 @@
         <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
@@ -6789,19 +6849,17 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>364</v>
+        <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6850,7 +6908,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6865,34 +6923,34 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6911,19 +6969,17 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>375</v>
+        <v>150</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>355</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6960,17 +7016,19 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6979,42 +7037,40 @@
         <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7024,7 +7080,7 @@
         <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
@@ -7033,19 +7089,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7094,7 +7150,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7103,40 +7159,40 @@
         <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7155,19 +7211,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>393</v>
+        <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>394</v>
+        <v>299</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>395</v>
+        <v>300</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>396</v>
+        <v>301</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>397</v>
+        <v>302</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7216,7 +7272,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>391</v>
+        <v>303</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7225,47 +7281,47 @@
         <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>400</v>
+        <v>373</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>401</v>
+        <v>306</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>402</v>
+        <v>307</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>404</v>
+        <v>374</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>404</v>
+        <v>374</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>405</v>
+        <v>375</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>92</v>
@@ -7277,19 +7333,17 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>406</v>
+        <v>376</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>407</v>
+        <v>377</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7326,23 +7380,25 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AC45" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>404</v>
+        <v>374</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
@@ -7351,36 +7407,34 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>82</v>
+        <v>381</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>412</v>
+        <v>383</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>414</v>
+        <v>385</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>415</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7390,7 +7444,7 @@
         <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>82</v>
@@ -7399,19 +7453,19 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>417</v>
+        <v>388</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7460,13 +7514,13 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
@@ -7475,36 +7529,34 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7523,19 +7575,19 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7572,71 +7624,71 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="D48" t="s" s="2">
-        <v>426</v>
+        <v>398</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
@@ -7645,19 +7697,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7706,80 +7758,80 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>425</v>
+        <v>397</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7828,49 +7880,49 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>360</v>
+        <v>426</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7886,22 +7938,22 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7938,19 +7990,17 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7965,64 +8015,68 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="D51" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8070,7 +8124,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8085,44 +8139,46 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="D52" t="s" s="2">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -8131,17 +8187,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8190,7 +8248,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>455</v>
+        <v>428</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8205,41 +8263,41 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>447</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>461</v>
+        <v>436</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8248,19 +8306,23 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>160</v>
+        <v>451</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>161</v>
+        <v>452</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8308,19 +8370,19 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>163</v>
+        <v>449</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8329,28 +8391,28 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>164</v>
+        <v>437</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8369,18 +8431,20 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>137</v>
+        <v>457</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>138</v>
+        <v>458</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>166</v>
+        <v>459</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8428,7 +8492,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>170</v>
+        <v>456</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8440,7 +8504,7 @@
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8452,10 +8516,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>82</v>
+        <v>462</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>164</v>
+        <v>384</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8463,14 +8527,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8480,16 +8544,16 @@
         <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>137</v>
+        <v>465</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>466</v>
@@ -8498,10 +8562,10 @@
         <v>467</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>140</v>
+        <v>468</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>146</v>
+        <v>469</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8550,7 +8614,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8562,10 +8626,10 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
@@ -8574,10 +8638,10 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>134</v>
+        <v>472</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8585,10 +8649,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8599,7 +8663,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8611,20 +8675,18 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>160</v>
+        <v>474</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -8672,13 +8734,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -8699,7 +8761,7 @@
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -8707,21 +8769,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8733,16 +8795,18 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -8790,13 +8854,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -8814,10 +8878,10 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8825,14 +8889,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8851,18 +8915,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>482</v>
+        <v>151</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>483</v>
+        <v>152</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>484</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -8910,7 +8972,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>480</v>
+        <v>153</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8922,7 +8984,7 @@
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -8934,10 +8996,10 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>486</v>
+        <v>154</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -8952,7 +9014,7 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8971,15 +9033,17 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>488</v>
+        <v>193</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9004,13 +9068,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9028,7 +9092,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>487</v>
+        <v>158</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9040,7 +9104,7 @@
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9052,10 +9116,10 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>492</v>
+        <v>154</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9063,14 +9127,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>489</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9083,25 +9147,25 @@
         <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>494</v>
+        <v>136</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>497</v>
+        <v>177</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>498</v>
+        <v>178</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9150,7 +9214,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9162,29 +9226,629 @@
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AK60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AO60" t="s" s="2">
+      <c r="AK61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AP60" t="s" s="2">
+      <c r="B62" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP60">
+  <autoFilter ref="A1:AP65">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9194,7 +9858,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI59">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2522" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2522" uniqueCount="526">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -468,11 +468,14 @@
     <t>extension-DiagnosticReport-note</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://va.gov/fhir/StructureDefinition/extension-DiagnosticReport-note}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-DiagnosticReport.note}
 </t>
   </si>
   <si>
-    <t>R5 pre-adopt for http://hl7.org/fhir/5.0/StructureDefinition/extension-DiagnosticReport.note</t>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -528,7 +531,7 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/StructureDefinition/extension-DiagnosticReport-note</t>
+    <t>http://hl7.org/fhir/5.0/StructureDefinition/extension-DiagnosticReport.note</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -538,6 +541,10 @@
   </si>
   <si>
     <t>DiagnosticReport.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
   </si>
   <si>
     <t>Value of extension</t>
@@ -3132,10 +3139,10 @@
         <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3195,7 +3202,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -3213,7 +3220,7 @@
         <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>82</v>
@@ -3221,10 +3228,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3247,13 +3254,13 @@
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3304,7 +3311,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3331,7 +3338,7 @@
         <v>82</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3339,10 +3346,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3413,7 +3420,7 @@
         <v>139</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>82</v>
@@ -3422,7 +3429,7 @@
         <v>140</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3457,10 +3464,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3486,13 +3493,13 @@
         <v>105</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3500,7 +3507,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>82</v>
@@ -3542,7 +3549,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>91</v>
@@ -3577,10 +3584,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3588,7 +3595,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>91</v>
@@ -3603,13 +3610,13 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3660,7 +3667,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3675,10 +3682,10 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>82</v>
@@ -3695,14 +3702,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3724,16 +3731,16 @@
         <v>136</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3782,7 +3789,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3817,14 +3824,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3843,19 +3850,19 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3904,7 +3911,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3925,24 +3932,24 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3965,13 +3972,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4022,7 +4029,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4049,7 +4056,7 @@
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -4057,14 +4064,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4086,13 +4093,13 @@
         <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4133,7 +4140,7 @@
         <v>139</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
@@ -4142,7 +4149,7 @@
         <v>140</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4169,7 +4176,7 @@
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -4177,10 +4184,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4206,16 +4213,16 @@
         <v>111</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4240,13 +4247,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -4264,7 +4271,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4291,7 +4298,7 @@
         <v>134</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4299,10 +4306,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4325,19 +4332,19 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4362,13 +4369,13 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4386,7 +4393,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4410,10 +4417,10 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4421,10 +4428,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4450,16 +4457,16 @@
         <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4469,10 +4476,10 @@
         <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>82</v>
@@ -4508,7 +4515,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4523,7 +4530,7 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
@@ -4532,10 +4539,10 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4543,10 +4550,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4569,16 +4576,16 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4592,7 +4599,7 @@
         <v>82</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>82</v>
@@ -4628,7 +4635,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4643,7 +4650,7 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
@@ -4652,10 +4659,10 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4663,10 +4670,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4689,13 +4696,13 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4746,7 +4753,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4770,10 +4777,10 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4781,10 +4788,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4807,16 +4814,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4866,7 +4873,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4890,10 +4897,10 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4901,14 +4908,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4927,19 +4934,19 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4988,7 +4995,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5003,19 +5010,19 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5023,10 +5030,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5052,14 +5059,14 @@
         <v>111</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5084,11 +5091,11 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5106,7 +5113,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -5115,40 +5122,40 @@
         <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5167,16 +5174,16 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5202,19 +5209,19 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
@@ -5224,7 +5231,7 @@
         <v>140</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5248,21 +5255,21 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5285,13 +5292,13 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5342,7 +5349,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5369,7 +5376,7 @@
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5377,14 +5384,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5406,13 +5413,13 @@
         <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5453,7 +5460,7 @@
         <v>139</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
@@ -5462,7 +5469,7 @@
         <v>140</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5489,7 +5496,7 @@
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5497,10 +5504,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5523,19 +5530,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5584,7 +5591,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5608,10 +5615,10 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5619,10 +5626,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5645,19 +5652,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5706,7 +5713,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5721,19 +5728,19 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5741,16 +5748,16 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5769,16 +5776,16 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5789,7 +5796,7 @@
         <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>82</v>
@@ -5804,13 +5811,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5828,7 +5835,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5843,7 +5850,7 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -5852,25 +5859,25 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5889,16 +5896,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5924,13 +5931,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5948,7 +5955,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>91</v>
@@ -5969,24 +5976,24 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6009,13 +6016,13 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6066,7 +6073,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6093,7 +6100,7 @@
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6101,14 +6108,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6130,13 +6137,13 @@
         <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6177,7 +6184,7 @@
         <v>139</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
@@ -6186,7 +6193,7 @@
         <v>140</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6213,7 +6220,7 @@
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6221,10 +6228,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6247,19 +6254,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6308,7 +6315,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6323,19 +6330,19 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6343,10 +6350,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6369,13 +6376,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6426,7 +6433,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6453,7 +6460,7 @@
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6461,14 +6468,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6490,13 +6497,13 @@
         <v>136</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6537,7 +6544,7 @@
         <v>139</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
@@ -6546,7 +6553,7 @@
         <v>140</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6573,7 +6580,7 @@
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6581,10 +6588,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6610,16 +6617,16 @@
         <v>105</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6629,7 +6636,7 @@
         <v>82</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>82</v>
@@ -6668,7 +6675,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6683,7 +6690,7 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
@@ -6692,10 +6699,10 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6703,10 +6710,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6729,16 +6736,16 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6788,7 +6795,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6812,10 +6819,10 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6823,10 +6830,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6852,14 +6859,14 @@
         <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6908,7 +6915,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6923,19 +6930,19 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6943,10 +6950,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6969,17 +6976,17 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7028,7 +7035,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7043,19 +7050,19 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7063,10 +7070,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7089,19 +7096,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7150,7 +7157,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7174,10 +7181,10 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -7185,10 +7192,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7211,19 +7218,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7272,7 +7279,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7287,19 +7294,19 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7307,14 +7314,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7333,17 +7340,17 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7392,7 +7399,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7407,34 +7414,34 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7453,19 +7460,19 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7514,7 +7521,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7535,28 +7542,28 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7575,19 +7582,19 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7624,7 +7631,7 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -7634,7 +7641,7 @@
         <v>140</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7643,7 +7650,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -7655,30 +7662,30 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7697,19 +7704,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7758,7 +7765,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7767,40 +7774,40 @@
         <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7819,19 +7826,19 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7880,7 +7887,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7889,40 +7896,40 @@
         <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7941,19 +7948,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7990,7 +7997,7 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8000,7 +8007,7 @@
         <v>140</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8021,30 +8028,30 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8063,19 +8070,19 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8124,7 +8131,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8139,36 +8146,36 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8187,19 +8194,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8248,7 +8255,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8263,34 +8270,34 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8309,19 +8316,19 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8370,7 +8377,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8391,24 +8398,24 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8431,19 +8438,19 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8492,7 +8499,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8516,10 +8523,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8527,14 +8534,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8553,19 +8560,19 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8614,7 +8621,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8629,7 +8636,7 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
@@ -8638,10 +8645,10 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8649,10 +8656,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8675,16 +8682,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8734,7 +8741,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8761,7 +8768,7 @@
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -8769,14 +8776,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8795,17 +8802,17 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8854,7 +8861,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8878,10 +8885,10 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8889,10 +8896,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8915,13 +8922,13 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8972,7 +8979,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8999,7 +9006,7 @@
         <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9007,14 +9014,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9036,13 +9043,13 @@
         <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9092,7 +9099,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9119,7 +9126,7 @@
         <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9127,14 +9134,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9156,16 +9163,16 @@
         <v>136</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9214,7 +9221,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9249,10 +9256,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9275,19 +9282,19 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9336,7 +9343,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9363,7 +9370,7 @@
         <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9371,10 +9378,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9397,13 +9404,13 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9454,7 +9461,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>91</v>
@@ -9481,7 +9488,7 @@
         <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
@@ -9489,14 +9496,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9515,17 +9522,17 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9574,7 +9581,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9598,10 +9605,10 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
@@ -9609,10 +9616,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9635,13 +9642,13 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9668,13 +9675,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9692,7 +9699,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9716,10 +9723,10 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>82</v>
@@ -9727,10 +9734,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9753,19 +9760,19 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9814,7 +9821,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9838,10 +9845,10 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -810,7 +810,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest)
 </t>
   </si>
   <si>
@@ -1192,7 +1192,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1400,7 +1400,7 @@
     <t>va-by</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>
@@ -1416,7 +1416,7 @@
     <t>va-at</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -853,7 +853,7 @@
     <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFDiagnosticReportLabStatus</t>
+    <t>http://va.gov/fhir/ValueSet/DiagnosticReportLabStatus</t>
   </si>
   <si>
     <t>us-core-8

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1214,7 +1214,8 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn</t>
+    <t>demographics.lrdfn
+accession.collected</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2025,7 +2025,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="121.93359375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2587" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2587" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1214,8 +1214,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn
-accession.collected</t>
+    <t>Patient.PatientExtension.VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1357,6 +1356,9 @@
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
   </si>
   <si>
+    <t>Documents.ToTime,LabOrder.Result.ResultTime</t>
+  </si>
+  <si>
     <t>OBR-22</t>
   </si>
   <si>
@@ -1417,6 +1419,9 @@
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
+    <t>Documents.Clinician,Documents.DocumentExtension.CareProviders,LabOrder.Result.VerifiedBy</t>
+  </si>
+  <si>
     <t>DiagnosticReport.performer:va-at</t>
   </si>
   <si>
@@ -1431,6 +1436,9 @@
   </si>
   <si>
     <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
+  </si>
+  <si>
+    <t>Documents.EnteredAt,LabOrder.Result.EnteredAt</t>
   </si>
   <si>
     <t>DiagnosticReport.resultsInterpreter</t>
@@ -2025,7 +2033,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="88.89453125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="121.93359375" customWidth="true" bestFit="true"/>
@@ -8060,31 +8068,31 @@
         <v>428</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>83</v>
+        <v>429</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8103,19 +8111,19 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8162,7 +8170,7 @@
         <v>141</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8186,30 +8194,30 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8228,19 +8236,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8289,7 +8297,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8304,39 +8312,39 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>83</v>
+        <v>449</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8355,19 +8363,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8416,7 +8424,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8431,37 +8439,37 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>83</v>
+        <v>455</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8480,19 +8488,19 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8541,7 +8549,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8565,24 +8573,24 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8605,19 +8613,19 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8666,7 +8674,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8693,7 +8701,7 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>388</v>
@@ -8704,14 +8712,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8730,19 +8738,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8791,7 +8799,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8806,7 +8814,7 @@
         <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
@@ -8818,10 +8826,10 @@
         <v>83</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>83</v>
@@ -8829,10 +8837,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8855,16 +8863,16 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8914,7 +8922,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8944,7 +8952,7 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -8952,14 +8960,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8978,17 +8986,17 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9037,7 +9045,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9064,10 +9072,10 @@
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9075,10 +9083,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9196,10 +9204,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9319,14 +9327,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9348,10 +9356,10 @@
         <v>137</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>180</v>
@@ -9406,7 +9414,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9444,10 +9452,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9473,16 +9481,16 @@
         <v>152</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9531,7 +9539,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9561,7 +9569,7 @@
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
@@ -9569,10 +9577,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9595,13 +9603,13 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9652,7 +9660,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>92</v>
@@ -9682,7 +9690,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -9690,14 +9698,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9719,14 +9727,14 @@
         <v>152</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9775,7 +9783,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9802,10 +9810,10 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -9813,10 +9821,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9842,10 +9850,10 @@
         <v>209</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9875,28 +9883,28 @@
         <v>283</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9923,10 +9931,10 @@
         <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -9934,10 +9942,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9960,19 +9968,19 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10021,7 +10029,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10048,10 +10056,10 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1214,7 +1214,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>Patient.PatientExtension.VeteranLrdfn</t>
+    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1419,7 +1419,7 @@
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
-    <t>Documents.Clinician,Documents.DocumentExtension.CareProviders,LabOrder.Result.VerifiedBy</t>
+    <t>Documents.Clinician,Documents.Extension[DocumentExtension].CareProviders,LabOrder.Result.VerifiedBy</t>
   </si>
   <si>
     <t>DiagnosticReport.performer:va-at</t>
@@ -2033,7 +2033,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="88.89453125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="99.32421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="121.93359375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-diagnosticreport-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-diagnosticreport-lab.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2587" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2587" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1389,6 +1389,10 @@
   </si>
   <si>
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -8160,7 +8164,7 @@
         <v>83</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>286</v>
+        <v>440</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8194,27 +8198,27 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>433</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>434</v>
@@ -8236,7 +8240,7 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>436</v>
@@ -8312,36 +8316,36 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>433</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>434</v>
@@ -8363,7 +8367,7 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>436</v>
@@ -8439,37 +8443,37 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8488,16 +8492,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>439</v>
@@ -8549,7 +8553,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8573,24 +8577,24 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8613,19 +8617,19 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8674,7 +8678,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8701,7 +8705,7 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>388</v>
@@ -8712,14 +8716,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8738,19 +8742,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8799,7 +8803,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8814,7 +8818,7 @@
         <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
@@ -8826,10 +8830,10 @@
         <v>83</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>83</v>
@@ -8837,10 +8841,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8863,16 +8867,16 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8922,7 +8926,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8952,7 +8956,7 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -8960,14 +8964,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8986,17 +8990,17 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9045,7 +9049,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9072,10 +9076,10 @@
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9083,10 +9087,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9204,10 +9208,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9327,14 +9331,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9356,10 +9360,10 @@
         <v>137</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>180</v>
@@ -9414,7 +9418,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9452,10 +9456,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9481,16 +9485,16 @@
         <v>152</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9539,7 +9543,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9569,7 +9573,7 @@
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
@@ -9577,10 +9581,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9603,13 +9607,13 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9660,7 +9664,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>92</v>
@@ -9690,7 +9694,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -9698,14 +9702,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9727,14 +9731,14 @@
         <v>152</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9783,7 +9787,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9810,10 +9814,10 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -9821,10 +9825,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9850,10 +9854,10 @@
         <v>209</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9883,10 +9887,10 @@
         <v>283</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -9904,7 +9908,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9931,10 +9935,10 @@
         <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -9942,10 +9946,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9968,19 +9972,19 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10029,7 +10033,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10056,10 +10060,10 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -559,7 +559,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>1442: source value from MICROBIOLOGY - BACT RPT REMARK &gt; BACT RPT REMARK - BACT RPT REMARK (63.05-13 &gt; 63.33-.01)</t>
+    <t>1442: source value based on MICROBIOLOGY - BACT RPT REMARK &gt; BACT RPT REMARK - BACT RPT REMARK (63.05-13 &gt; 63.33-.01)</t>
   </si>
   <si>
     <t>Micro.BacteriologyReports.BacteriologyReportRemark</t>
@@ -750,7 +750,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1605: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - IEN (63.05-.35 &gt; 63.5-.001)</t>
+    <t>1605: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - IEN (63.05-.35 &gt; 63.5-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -829,7 +829,7 @@
     <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
-    <t>1690: reference from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.05-.35 &gt; 63.5-3)</t>
+    <t>1690: reference based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.05-.35 &gt; 63.5-3)</t>
   </si>
   <si>
     <t>Micro.MicroOrderedTest.CPRSOrderIEN,SStaff.SMicroOrderedTest.CPRSOrderIEN</t>
@@ -971,7 +971,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+    <t>1662: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>Dim.LabChemTest.NationalVALabCodeIEN</t>
@@ -1043,7 +1043,7 @@
     <t>DiagnosticReport.code.coding</t>
   </si>
   <si>
-    <t>1420: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
+    <t>1420: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
   </si>
   <si>
     <t>DiagnosticReport.code.coding.id</t>
@@ -1118,7 +1118,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1420-1: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - CODE (60-64 &gt; 64-25 &gt; 95.3-.01)</t>
+    <t>1420-1: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - CODE (60-64 &gt; 64-25 &gt; 95.3-.01)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1142,7 +1142,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1420-3: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - COMPONENT (60-64 &gt; 64-25 &gt; 95.3-1)</t>
+    <t>1420-3: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - COMPONENT (60-64 &gt; 64-25 &gt; 95.3-1)</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -1182,7 +1182,7 @@
     <t>DiagnosticReport.code.text</t>
   </si>
   <si>
-    <t>1661: source value from LABORATORY TEST - NAME (60-.01)</t>
+    <t>1661: source value based on LABORATORY TEST - NAME (60-.01)</t>
   </si>
   <si>
     <t>Dim.LabChemTest.LabChemTestName</t>
@@ -1208,7 +1208,7 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
-    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+    <t>1421: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
@@ -1317,7 +1317,7 @@
 </t>
   </si>
   <si>
-    <t>1424: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
+    <t>1424: source value based on MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime</t>
@@ -1350,7 +1350,7 @@
 </t>
   </si>
   <si>
-    <t>1429: source value from MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
+    <t>1429: source value based on MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
@@ -1417,7 +1417,7 @@
 </t>
   </si>
   <si>
-    <t>1434: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
+    <t>1434: reference based on MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
@@ -1436,7 +1436,7 @@
 </t>
   </si>
   <si>
-    <t>1682: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
+    <t>1682: reference based on MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
   </si>
   <si>
     <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
@@ -1513,7 +1513,7 @@
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
   </si>
   <si>
-    <t>1437: reference from See mapping for Lab Observation</t>
+    <t>1437: reference based on See mapping for Lab Observation</t>
   </si>
   <si>
     <t>OBXs</t>
@@ -2035,7 +2035,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="167.57421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="99.32421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2587" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -854,6 +854,9 @@
   </si>
   <si>
     <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_DiagnosticReportLabStatus](ConceptMap-VF-DiagnosticReportLabStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/DiagnosticReportLabStatus</t>
@@ -5188,9 +5191,11 @@
       <c r="X26" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="Y26" s="2"/>
+      <c r="Y26" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5217,43 +5222,43 @@
         <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5275,13 +5280,13 @@
         <v>209</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5307,19 +5312,19 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
@@ -5329,7 +5334,7 @@
         <v>141</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5356,21 +5361,21 @@
         <v>83</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5488,10 +5493,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5611,10 +5616,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5637,19 +5642,19 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5698,7 +5703,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5725,10 +5730,10 @@
         <v>83</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>83</v>
@@ -5736,10 +5741,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5765,16 +5770,16 @@
         <v>152</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5823,7 +5828,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5838,10 +5843,10 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>83</v>
@@ -5850,10 +5855,10 @@
         <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -5861,16 +5866,16 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5892,13 +5897,13 @@
         <v>209</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5909,7 +5914,7 @@
         <v>83</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>83</v>
@@ -5924,13 +5929,13 @@
         <v>83</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>83</v>
@@ -5948,7 +5953,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5963,7 +5968,7 @@
         <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
@@ -5975,25 +5980,25 @@
         <v>83</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6015,13 +6020,13 @@
         <v>209</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6050,10 +6055,10 @@
         <v>214</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -6071,7 +6076,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>92</v>
@@ -6095,24 +6100,24 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6230,10 +6235,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6353,10 +6358,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6379,19 +6384,19 @@
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6440,7 +6445,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6455,10 +6460,10 @@
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>83</v>
@@ -6467,10 +6472,10 @@
         <v>83</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
@@ -6478,10 +6483,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6599,10 +6604,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6722,10 +6727,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6751,16 +6756,16 @@
         <v>106</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6770,7 +6775,7 @@
         <v>83</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>83</v>
@@ -6809,7 +6814,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6824,7 +6829,7 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
@@ -6836,10 +6841,10 @@
         <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -6847,10 +6852,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6876,13 +6881,13 @@
         <v>152</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6932,7 +6937,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6959,10 +6964,10 @@
         <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>83</v>
@@ -6970,10 +6975,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6999,14 +7004,14 @@
         <v>112</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7055,7 +7060,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7070,10 +7075,10 @@
         <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>83</v>
@@ -7082,10 +7087,10 @@
         <v>83</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7093,10 +7098,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7122,14 +7127,14 @@
         <v>152</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7178,7 +7183,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7193,10 +7198,10 @@
         <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>83</v>
@@ -7205,10 +7210,10 @@
         <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -7216,10 +7221,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7242,19 +7247,19 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7303,7 +7308,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7330,10 +7335,10 @@
         <v>83</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>83</v>
@@ -7341,10 +7346,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7370,16 +7375,16 @@
         <v>152</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7428,7 +7433,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7443,10 +7448,10 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>83</v>
@@ -7455,10 +7460,10 @@
         <v>83</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>83</v>
@@ -7466,14 +7471,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7492,17 +7497,17 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7551,7 +7556,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7566,37 +7571,37 @@
         <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7615,19 +7620,19 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7676,7 +7681,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7700,28 +7705,28 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7740,19 +7745,19 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7789,7 +7794,7 @@
         <v>83</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -7799,7 +7804,7 @@
         <v>141</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7808,7 +7813,7 @@
         <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>104</v>
@@ -7823,30 +7828,30 @@
         <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7865,19 +7870,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7926,7 +7931,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7935,43 +7940,43 @@
         <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7990,19 +7995,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8051,7 +8056,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8060,43 +8065,43 @@
         <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8115,19 +8120,19 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8164,7 +8169,7 @@
         <v>83</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8174,7 +8179,7 @@
         <v>141</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8198,30 +8203,30 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8240,19 +8245,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8301,7 +8306,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8316,39 +8321,39 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8367,19 +8372,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8428,7 +8433,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8443,37 +8448,37 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8492,19 +8497,19 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8553,7 +8558,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8577,24 +8582,24 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8617,19 +8622,19 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8678,7 +8683,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8705,10 +8710,10 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>83</v>
@@ -8716,14 +8721,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8742,19 +8747,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8803,7 +8808,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8818,7 +8823,7 @@
         <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
@@ -8830,10 +8835,10 @@
         <v>83</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>83</v>
@@ -8841,10 +8846,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8867,16 +8872,16 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8926,7 +8931,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8956,7 +8961,7 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -8964,14 +8969,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8990,17 +8995,17 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9049,7 +9054,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9076,10 +9081,10 @@
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9087,10 +9092,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9208,10 +9213,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9331,14 +9336,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9360,10 +9365,10 @@
         <v>137</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>180</v>
@@ -9418,7 +9423,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9456,10 +9461,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9485,16 +9490,16 @@
         <v>152</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9543,7 +9548,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9573,7 +9578,7 @@
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
@@ -9581,10 +9586,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9607,13 +9612,13 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9664,7 +9669,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>92</v>
@@ -9694,7 +9699,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -9702,14 +9707,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9731,14 +9736,14 @@
         <v>152</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9787,7 +9792,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9814,10 +9819,10 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -9825,10 +9830,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9854,10 +9859,10 @@
         <v>209</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9884,13 +9889,13 @@
         <v>83</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -9908,7 +9913,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9935,10 +9940,10 @@
         <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -9946,10 +9951,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9972,19 +9977,19 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10033,7 +10038,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10060,10 +10065,10 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1500,7 +1500,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationObservation)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyBacteriologyObservation)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1211,13 +1211,11 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
-    <t>1421: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
-  </si>
-  <si>
-    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lombdr-54-1421:If PATIENT - LABORATORY REFERENCE (2-63) == LAB DATA – LRDFN (63-.01) then reference /Patient based on (2-) {true}</t>
+  </si>
+  <si>
+    <t>1421: reference based on PATIENT - (2-) if PATIENT - LABORATORY REFERENCE (2-63) == LAB DATA – LRDFN (63-.01)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -7568,40 +7566,40 @@
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>384</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AP45" t="s" s="2">
+      <c r="AQ45" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>390</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7620,19 +7618,19 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7681,7 +7679,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7705,28 +7703,28 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>401</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7745,19 +7743,19 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7794,7 +7792,7 @@
         <v>83</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -7804,7 +7802,7 @@
         <v>141</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7813,7 +7811,7 @@
         <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>104</v>
@@ -7828,30 +7826,30 @@
         <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AP47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>414</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="B48" t="s" s="2">
+      <c r="D48" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="D48" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7870,19 +7868,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7931,7 +7929,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7940,43 +7938,43 @@
         <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AM48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AP48" t="s" s="2">
+      <c r="AQ48" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>414</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7995,19 +7993,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8056,7 +8054,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8065,43 +8063,43 @@
         <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AN49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AP49" t="s" s="2">
+      <c r="AQ49" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>433</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8120,19 +8118,19 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8169,7 +8167,7 @@
         <v>83</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8179,7 +8177,7 @@
         <v>141</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8203,30 +8201,30 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="B51" t="s" s="2">
+      <c r="D51" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="D51" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8245,19 +8243,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8306,7 +8304,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8321,39 +8319,39 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="AN51" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AO51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AP51" t="s" s="2">
+      <c r="AQ51" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="B52" t="s" s="2">
+      <c r="D52" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="D52" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8372,19 +8370,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8433,7 +8431,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8448,37 +8446,37 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>457</v>
-      </c>
       <c r="AN52" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AP52" t="s" s="2">
+      <c r="AQ52" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AQ52" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8497,19 +8495,19 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="N53" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="O53" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8558,7 +8556,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8582,24 +8580,24 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AP53" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8622,19 +8620,19 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8683,7 +8681,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8710,10 +8708,10 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>83</v>
@@ -8721,14 +8719,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8747,19 +8745,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8808,7 +8806,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8823,22 +8821,22 @@
         <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO55" t="s" s="2">
+      <c r="AP55" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>83</v>
@@ -8846,10 +8844,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8872,16 +8870,16 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8931,7 +8929,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8961,7 +8959,7 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -8969,14 +8967,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8995,17 +8993,17 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9054,7 +9052,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9081,10 +9079,10 @@
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9092,10 +9090,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9213,10 +9211,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9336,14 +9334,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9365,10 +9363,10 @@
         <v>137</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>180</v>
@@ -9423,7 +9421,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9461,10 +9459,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9490,16 +9488,16 @@
         <v>152</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9548,7 +9546,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9578,7 +9576,7 @@
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
@@ -9586,10 +9584,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9612,13 +9610,13 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9669,7 +9667,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>92</v>
@@ -9699,7 +9697,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -9707,14 +9705,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9736,14 +9734,14 @@
         <v>152</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9792,7 +9790,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9819,10 +9817,10 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -9830,10 +9828,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9859,10 +9857,10 @@
         <v>209</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9892,11 +9890,11 @@
         <v>284</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>524</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
       </c>
@@ -9913,7 +9911,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9940,10 +9938,10 @@
         <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -9951,10 +9949,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9977,19 +9975,19 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10038,7 +10036,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10065,10 +10063,10 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
